--- a/diseases/d020/2005-2009.xlsx
+++ b/diseases/d020/2005-2009.xlsx
@@ -1061,9 +1061,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -1505,9 +1502,6 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -1949,9 +1943,6 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
@@ -2393,9 +2384,6 @@
       <c r="O13" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
@@ -2837,9 +2825,6 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
@@ -3429,9 +3414,6 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
@@ -4021,9 +4003,6 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
@@ -4613,9 +4592,6 @@
       <c r="O28" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
@@ -5205,9 +5181,6 @@
       <c r="O32" t="n">
         <v>3</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.00626937707720136</v>
       </c>
@@ -5797,9 +5770,6 @@
       <c r="O36" t="n">
         <v>2</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0.004179584718134241</v>
       </c>
@@ -6389,9 +6359,6 @@
       <c r="O40" t="n">
         <v>1</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0.00208979235906712</v>
       </c>
@@ -6833,9 +6800,6 @@
       <c r="O43" t="n">
         <v>0</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
@@ -7277,9 +7241,6 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
@@ -7721,9 +7682,6 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
@@ -8165,9 +8123,6 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
@@ -8609,9 +8564,6 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
@@ -9053,9 +9005,6 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
@@ -9645,9 +9594,6 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
@@ -10237,9 +10183,6 @@
       <c r="O66" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
@@ -10829,9 +10772,6 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
@@ -11421,9 +11361,6 @@
       <c r="O74" t="n">
         <v>0</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0</v>
       </c>
@@ -12013,9 +11950,6 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0</v>
       </c>
@@ -12605,9 +12539,6 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
@@ -13197,9 +13128,6 @@
       <c r="O86" t="n">
         <v>0</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0</v>
       </c>
@@ -13641,9 +13569,6 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0</v>
       </c>
@@ -14085,9 +14010,6 @@
       <c r="O92" t="n">
         <v>0</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0</v>
       </c>
@@ -14529,9 +14451,6 @@
       <c r="O95" t="n">
         <v>0</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0</v>
       </c>
@@ -14973,9 +14892,6 @@
       <c r="O98" t="n">
         <v>0</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
@@ -15417,9 +15333,6 @@
       <c r="O101" t="n">
         <v>0</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0</v>
       </c>
@@ -16009,9 +15922,6 @@
       <c r="O105" t="n">
         <v>0</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0</v>
       </c>
@@ -16601,9 +16511,6 @@
       <c r="O109" t="n">
         <v>0</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0</v>
       </c>
@@ -17193,9 +17100,6 @@
       <c r="O113" t="n">
         <v>0</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0</v>
       </c>
@@ -17785,9 +17689,6 @@
       <c r="O117" t="n">
         <v>3</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0.006226893231623397</v>
       </c>
@@ -18229,9 +18130,6 @@
       <c r="O120" t="n">
         <v>1</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0.002075631077207799</v>
       </c>
@@ -18821,9 +18719,6 @@
       <c r="O124" t="n">
         <v>3</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0.006226893231623397</v>
       </c>
@@ -19265,9 +19160,6 @@
       <c r="O127" t="n">
         <v>0</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0</v>
       </c>
@@ -19709,9 +19601,6 @@
       <c r="O130" t="n">
         <v>0</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0</v>
       </c>
@@ -20153,9 +20042,6 @@
       <c r="O133" t="n">
         <v>0</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0</v>
       </c>
@@ -20597,9 +20483,6 @@
       <c r="O136" t="n">
         <v>0</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0</v>
       </c>
@@ -21041,9 +20924,6 @@
       <c r="O139" t="n">
         <v>0</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0</v>
       </c>
@@ -21485,9 +21365,6 @@
       <c r="O142" t="n">
         <v>0</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0</v>
       </c>
@@ -22077,9 +21954,6 @@
       <c r="O146" t="n">
         <v>0</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0</v>
       </c>
@@ -22669,9 +22543,6 @@
       <c r="O150" t="n">
         <v>0</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0</v>
       </c>
@@ -23261,9 +23132,6 @@
       <c r="O154" t="n">
         <v>0</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0</v>
       </c>
@@ -23705,9 +23573,6 @@
       <c r="O157" t="n">
         <v>1</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>0.002067974615115286</v>
       </c>
@@ -24149,9 +24014,6 @@
       <c r="O160" t="n">
         <v>3</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0.006203923845345857</v>
       </c>
@@ -24593,9 +24455,6 @@
       <c r="O163" t="n">
         <v>2</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0.004135949230230571</v>
       </c>
@@ -25185,9 +25044,6 @@
       <c r="O167" t="n">
         <v>0</v>
       </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
       <c r="R167" t="n">
         <v>0</v>
       </c>
@@ -25629,9 +25485,6 @@
       <c r="O170" t="n">
         <v>0</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0</v>
       </c>
@@ -26073,9 +25926,6 @@
       <c r="O173" t="n">
         <v>0</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>0</v>
       </c>
@@ -26517,9 +26367,6 @@
       <c r="O176" t="n">
         <v>0</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>0</v>
       </c>
@@ -27109,9 +26956,6 @@
       <c r="O180" t="n">
         <v>0</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0</v>
       </c>
@@ -27553,9 +27397,6 @@
       <c r="O183" t="n">
         <v>0</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="R183" t="n">
         <v>0</v>
       </c>
@@ -28145,9 +27986,6 @@
       <c r="O187" t="n">
         <v>0</v>
       </c>
-      <c r="Q187" t="n">
-        <v>0</v>
-      </c>
       <c r="R187" t="n">
         <v>0</v>
       </c>
@@ -28589,9 +28427,6 @@
       <c r="O190" t="n">
         <v>0</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0</v>
       </c>
@@ -29181,9 +29016,6 @@
       <c r="O194" t="n">
         <v>0</v>
       </c>
-      <c r="Q194" t="n">
-        <v>0</v>
-      </c>
       <c r="R194" t="n">
         <v>0</v>
       </c>
@@ -29773,9 +29605,6 @@
       <c r="O198" t="n">
         <v>1</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>0.002059872819538363</v>
       </c>
@@ -30217,9 +30046,6 @@
       <c r="O201" t="n">
         <v>1</v>
       </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
       <c r="R201" t="n">
         <v>0.002059872819538363</v>
       </c>
@@ -30809,9 +30635,6 @@
       <c r="O205" t="n">
         <v>3</v>
       </c>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
       <c r="R205" t="n">
         <v>0.00617961845861509</v>
       </c>
@@ -31252,9 +31075,6 @@
       </c>
       <c r="O208" t="n">
         <v>1</v>
-      </c>
-      <c r="Q208" t="n">
-        <v>0</v>
       </c>
       <c r="R208" t="n">
         <v>0.002059872819538363</v>
